--- a/inventories/baseline/lci-Salar-de-Cauchari-Olaroz.xlsx
+++ b/inventories/baseline/lci-Salar-de-Cauchari-Olaroz.xlsx
@@ -856,7 +856,7 @@
         <v>3</v>
       </c>
       <c r="B28">
-        <v>-0.03969358402037569</v>
+        <v>-0.03969358402037568</v>
       </c>
       <c r="C28" t="s">
         <v>1</v>
@@ -941,7 +941,7 @@
         <v>35</v>
       </c>
       <c r="B33">
-        <v>0.0003707875609385736</v>
+        <v>0.0003707875609385735</v>
       </c>
       <c r="C33" t="s">
         <v>31</v>
@@ -1222,7 +1222,7 @@
         <v>3</v>
       </c>
       <c r="B60">
-        <v>0.2297858423956253</v>
+        <v>0.202984983352535</v>
       </c>
       <c r="C60" t="s">
         <v>1</v>
@@ -1239,7 +1239,7 @@
         <v>41</v>
       </c>
       <c r="B61">
-        <v>0.7127676970054684</v>
+        <v>0.7462687708093314</v>
       </c>
       <c r="C61" t="s">
         <v>1</v>
@@ -1256,7 +1256,7 @@
         <v>39</v>
       </c>
       <c r="B62">
-        <v>0.2039578503467862</v>
+        <v>0.2135441531857777</v>
       </c>
       <c r="C62" t="s">
         <v>1</v>
@@ -1273,7 +1273,7 @@
         <v>42</v>
       </c>
       <c r="B63">
-        <v>0.05744646059890633</v>
+        <v>0.05074624583813374</v>
       </c>
       <c r="C63" t="s">
         <v>33</v>
@@ -1388,7 +1388,7 @@
         <v>3</v>
       </c>
       <c r="B75">
-        <v>0.0005860508005212916</v>
+        <v>0.0005860508005212914</v>
       </c>
       <c r="C75" t="s">
         <v>1</v>
@@ -1405,7 +1405,7 @@
         <v>44</v>
       </c>
       <c r="B76">
-        <v>0.9975896281979559</v>
+        <v>0.9975896281979558</v>
       </c>
       <c r="C76" t="s">
         <v>1</v>
@@ -1422,7 +1422,7 @@
         <v>45</v>
       </c>
       <c r="B77">
-        <v>0.001824321001522815</v>
+        <v>0.001824321001522814</v>
       </c>
       <c r="C77" t="s">
         <v>31</v>
@@ -1520,7 +1520,7 @@
         <v>27</v>
       </c>
       <c r="B88">
-        <v>-0.0536453965479881</v>
+        <v>-0.05364539654798816</v>
       </c>
       <c r="D88" t="s">
         <v>28</v>
@@ -1852,7 +1852,7 @@
         <v>40</v>
       </c>
       <c r="B118">
-        <v>21.64071487459576</v>
+        <v>24.49801859907103</v>
       </c>
       <c r="C118" t="s">
         <v>1</v>
@@ -1869,7 +1869,7 @@
         <v>22</v>
       </c>
       <c r="B119">
-        <v>0.02305977814506105</v>
+        <v>0.02610444604819045</v>
       </c>
       <c r="C119" t="s">
         <v>23</v>
@@ -2018,7 +2018,7 @@
         <v>22</v>
       </c>
       <c r="B133">
-        <v>4.251955821430681E-05</v>
+        <v>4.25195582143068E-05</v>
       </c>
       <c r="C133" t="s">
         <v>23</v>
@@ -2035,7 +2035,7 @@
         <v>36</v>
       </c>
       <c r="B134">
-        <v>-0.004251955821430681</v>
+        <v>-0.00425195582143068</v>
       </c>
       <c r="C134" t="s">
         <v>31</v>
@@ -2580,7 +2580,7 @@
         <v>54</v>
       </c>
       <c r="B187">
-        <v>0.07547169809937244</v>
+        <v>0.06355379532311731</v>
       </c>
       <c r="D187" t="s">
         <v>11</v>
@@ -2597,7 +2597,7 @@
         <v>55</v>
       </c>
       <c r="B188">
-        <v>1.119094632935327E-10</v>
+        <v>9.423759242189659E-11</v>
       </c>
       <c r="D188" t="s">
         <v>56</v>
@@ -2614,7 +2614,7 @@
         <v>58</v>
       </c>
       <c r="B189">
-        <v>2.797736582338318E-12</v>
+        <v>2.355939810547415E-12</v>
       </c>
       <c r="D189" t="s">
         <v>59</v>
@@ -2631,7 +2631,7 @@
         <v>60</v>
       </c>
       <c r="B190">
-        <v>2.797736582338318E-12</v>
+        <v>2.355939810547415E-12</v>
       </c>
       <c r="D190" t="s">
         <v>59</v>
@@ -2682,7 +2682,7 @@
         <v>3</v>
       </c>
       <c r="B193">
-        <v>0.4088794123841791</v>
+        <v>0.5022245718235788</v>
       </c>
       <c r="C193" t="s">
         <v>1</v>
@@ -2699,7 +2699,7 @@
         <v>61</v>
       </c>
       <c r="B194">
-        <v>0.0003365828954722993</v>
+        <v>0.0002834323459893976</v>
       </c>
       <c r="C194" t="s">
         <v>1</v>
@@ -2716,7 +2716,7 @@
         <v>22</v>
       </c>
       <c r="B195">
-        <v>0.004763951491679999</v>
+        <v>0.004012163629236762</v>
       </c>
       <c r="C195" t="s">
         <v>23</v>
@@ -2733,7 +2733,7 @@
         <v>45</v>
       </c>
       <c r="B196">
-        <v>5.706460158915793E-10</v>
+        <v>0.49156585817333</v>
       </c>
       <c r="C196" t="s">
         <v>31</v>
@@ -2750,7 +2750,7 @@
         <v>63</v>
       </c>
       <c r="B197">
-        <v>0.0007359829419615531</v>
+        <v>0.0006197622477387878</v>
       </c>
       <c r="C197" t="s">
         <v>31</v>
@@ -2767,7 +2767,7 @@
         <v>64</v>
       </c>
       <c r="B198">
-        <v>-44.08331142400993</v>
+        <v>-37.12201821294467</v>
       </c>
       <c r="C198" t="s">
         <v>31</v>
@@ -2784,7 +2784,7 @@
         <v>48</v>
       </c>
       <c r="B199">
-        <v>-0.0004088794122008629</v>
+        <v>-0.0003443123598548821</v>
       </c>
       <c r="C199" t="s">
         <v>1</v>
@@ -2950,7 +2950,7 @@
         <v>3</v>
       </c>
       <c r="B214">
-        <v>0.6411388800275167</v>
+        <v>0.6395693279609911</v>
       </c>
       <c r="C214" t="s">
         <v>1</v>
@@ -3316,7 +3316,7 @@
         <v>50</v>
       </c>
       <c r="B246">
-        <v>0.9659292326363347</v>
+        <v>0.9659292326363348</v>
       </c>
       <c r="C246" t="s">
         <v>1</v>
@@ -3333,7 +3333,7 @@
         <v>71</v>
       </c>
       <c r="B247">
-        <v>0.006562086665157993</v>
+        <v>0.006562086665157992</v>
       </c>
       <c r="C247" t="s">
         <v>31</v>
@@ -3465,7 +3465,7 @@
         <v>65</v>
       </c>
       <c r="B260">
-        <v>1.225281657903964</v>
+        <v>1.227642590598365</v>
       </c>
       <c r="C260" t="s">
         <v>1</v>
@@ -3482,7 +3482,7 @@
         <v>39</v>
       </c>
       <c r="B261">
-        <v>0.1299993954117621</v>
+        <v>0.1302498846122656</v>
       </c>
       <c r="C261" t="s">
         <v>1</v>
@@ -3499,7 +3499,7 @@
         <v>22</v>
       </c>
       <c r="B262">
-        <v>0.001793095109127753</v>
+        <v>0.001796550132582973</v>
       </c>
       <c r="C262" t="s">
         <v>23</v>
@@ -3516,7 +3516,7 @@
         <v>72</v>
       </c>
       <c r="B263">
-        <v>0.002816020723799551</v>
+        <v>0.002845532382479561</v>
       </c>
       <c r="C263" t="s">
         <v>31</v>
